--- a/accord/data/hotel_weather_data.xlsx
+++ b/accord/data/hotel_weather_data.xlsx
@@ -441,22 +441,22 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>annee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mois</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>hotel_lat</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>hotel_lon</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>annee</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>mois</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -592,16 +592,16 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>4.338978494623656</v>
@@ -688,16 +688,16 @@
         </is>
       </c>
       <c r="C3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F3" t="n">
-        <v>2</v>
       </c>
       <c r="G3" t="n">
         <v>4.786011904761905</v>
@@ -784,16 +784,16 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F4" t="n">
-        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>8.256317204301075</v>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F5" t="n">
-        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>13.05652777777778</v>
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>16.08051075268817</v>
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F7" t="n">
-        <v>6</v>
       </c>
       <c r="G7" t="n">
         <v>21.65291666666667</v>
@@ -1168,16 +1168,16 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F8" t="n">
-        <v>7</v>
       </c>
       <c r="G8" t="n">
         <v>20.70013440860215</v>
@@ -1264,16 +1264,16 @@
         </is>
       </c>
       <c r="C9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F9" t="n">
-        <v>8</v>
       </c>
       <c r="G9" t="n">
         <v>21.14408602150537</v>
@@ -1360,16 +1360,16 @@
         </is>
       </c>
       <c r="C10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E10" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F10" t="n">
-        <v>9</v>
       </c>
       <c r="G10" t="n">
         <v>15.73041666666667</v>
@@ -1456,16 +1456,16 @@
         </is>
       </c>
       <c r="C11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F11" t="n">
-        <v>10</v>
       </c>
       <c r="G11" t="n">
         <v>12.45094086021505</v>
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E12" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F12" t="n">
-        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>8.55486111111111</v>
@@ -1648,16 +1648,16 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F13" t="n">
-        <v>12</v>
       </c>
       <c r="G13" t="n">
         <v>6.360618279569893</v>
@@ -1744,16 +1744,16 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1</v>
       </c>
       <c r="G14" t="n">
         <v>4.91989247311828</v>
@@ -1840,16 +1840,16 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>8.523809523809524</v>
@@ -1936,16 +1936,16 @@
         </is>
       </c>
       <c r="C16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E16" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F16" t="n">
-        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>9.261290322580646</v>
@@ -2032,16 +2032,16 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F17" t="n">
-        <v>4</v>
       </c>
       <c r="G17" t="n">
         <v>13.29361111111111</v>
@@ -2128,16 +2128,16 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F18" t="n">
-        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>16.67110215053764</v>
@@ -2224,16 +2224,16 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F19" t="n">
-        <v>6</v>
       </c>
       <c r="G19" t="n">
         <v>22.68513888888889</v>
@@ -2320,16 +2320,16 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F20" t="n">
-        <v>7</v>
       </c>
       <c r="G20" t="n">
         <v>25.78049535603715</v>
@@ -2416,16 +2416,16 @@
         </is>
       </c>
       <c r="C21" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D21" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F21" t="n">
-        <v>8</v>
       </c>
       <c r="G21" t="n">
         <v>21.14408602150537</v>
@@ -2512,16 +2512,16 @@
         </is>
       </c>
       <c r="C22" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F22" t="n">
-        <v>9</v>
       </c>
       <c r="G22" t="n">
         <v>15.73041666666667</v>
@@ -2608,16 +2608,16 @@
         </is>
       </c>
       <c r="C23" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F23" t="n">
-        <v>10</v>
       </c>
       <c r="G23" t="n">
         <v>12.45094086021505</v>
@@ -2704,16 +2704,16 @@
         </is>
       </c>
       <c r="C24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11</v>
+      </c>
+      <c r="E24" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F24" t="n">
-        <v>11</v>
       </c>
       <c r="G24" t="n">
         <v>8.55486111111111</v>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="C25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D25" t="n">
+        <v>12</v>
+      </c>
+      <c r="E25" t="n">
         <v>48.885048</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>2.329923</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F25" t="n">
-        <v>12</v>
       </c>
       <c r="G25" t="n">
         <v>6.360618279569893</v>
@@ -2896,16 +2896,16 @@
         </is>
       </c>
       <c r="C26" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1</v>
       </c>
       <c r="G26" t="n">
         <v>4.103763440860215</v>
@@ -2986,16 +2986,16 @@
         </is>
       </c>
       <c r="C27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E27" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2</v>
       </c>
       <c r="G27" t="n">
         <v>4.922619047619047</v>
@@ -3076,16 +3076,16 @@
         </is>
       </c>
       <c r="C28" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F28" t="n">
-        <v>3</v>
       </c>
       <c r="G28" t="n">
         <v>8.99744623655914</v>
@@ -3166,16 +3166,16 @@
         </is>
       </c>
       <c r="C29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F29" t="n">
-        <v>4</v>
       </c>
       <c r="G29" t="n">
         <v>13.36944444444444</v>
@@ -3256,16 +3256,16 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5</v>
       </c>
       <c r="G30" t="n">
         <v>15.67741935483871</v>
@@ -3346,16 +3346,16 @@
         </is>
       </c>
       <c r="C31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F31" t="n">
-        <v>6</v>
       </c>
       <c r="G31" t="n">
         <v>21.10138888888889</v>
@@ -3436,16 +3436,16 @@
         </is>
       </c>
       <c r="C32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7</v>
+      </c>
+      <c r="E32" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F32" t="n">
-        <v>7</v>
       </c>
       <c r="G32" t="n">
         <v>20.64784946236559</v>
@@ -3526,16 +3526,16 @@
         </is>
       </c>
       <c r="C33" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E33" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F33" t="n">
-        <v>8</v>
       </c>
       <c r="G33" t="n">
         <v>20.86290322580645</v>
@@ -3616,16 +3616,16 @@
         </is>
       </c>
       <c r="C34" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9</v>
+      </c>
+      <c r="E34" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E34" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F34" t="n">
-        <v>9</v>
       </c>
       <c r="G34" t="n">
         <v>16.15972222222222</v>
@@ -3706,16 +3706,16 @@
         </is>
       </c>
       <c r="C35" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E35" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F35" t="n">
-        <v>10</v>
       </c>
       <c r="G35" t="n">
         <v>12.74865591397849</v>
@@ -3796,16 +3796,16 @@
         </is>
       </c>
       <c r="C36" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D36" t="n">
+        <v>11</v>
+      </c>
+      <c r="E36" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E36" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F36" t="n">
-        <v>11</v>
       </c>
       <c r="G36" t="n">
         <v>8.83611111111111</v>
@@ -3886,16 +3886,16 @@
         </is>
       </c>
       <c r="C37" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D37" t="n">
+        <v>12</v>
+      </c>
+      <c r="E37" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E37" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F37" t="n">
-        <v>12</v>
       </c>
       <c r="G37" t="n">
         <v>6.840725806451613</v>
@@ -3976,16 +3976,16 @@
         </is>
       </c>
       <c r="C38" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E38" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
       </c>
       <c r="G38" t="n">
         <v>5.184139784946237</v>
@@ -4066,16 +4066,16 @@
         </is>
       </c>
       <c r="C39" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E39" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F39" t="n">
-        <v>2</v>
       </c>
       <c r="G39" t="n">
         <v>8.960863095238096</v>
@@ -4156,16 +4156,16 @@
         </is>
       </c>
       <c r="C40" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F40" t="n">
-        <v>3</v>
       </c>
       <c r="G40" t="n">
         <v>9.90510752688172</v>
@@ -4246,16 +4246,16 @@
         </is>
       </c>
       <c r="C41" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D41" t="n">
+      <c r="F41" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E41" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F41" t="n">
-        <v>4</v>
       </c>
       <c r="G41" t="n">
         <v>13.07375</v>
@@ -4336,16 +4336,16 @@
         </is>
       </c>
       <c r="C42" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E42" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D42" t="n">
+      <c r="F42" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E42" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F42" t="n">
-        <v>5</v>
       </c>
       <c r="G42" t="n">
         <v>16.99059139784946</v>
@@ -4426,16 +4426,16 @@
         </is>
       </c>
       <c r="C43" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D43" t="n">
+        <v>6</v>
+      </c>
+      <c r="E43" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D43" t="n">
+      <c r="F43" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E43" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F43" t="n">
-        <v>6</v>
       </c>
       <c r="G43" t="n">
         <v>22.25416666666667</v>
@@ -4516,16 +4516,16 @@
         </is>
       </c>
       <c r="C44" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D44" t="n">
+        <v>7</v>
+      </c>
+      <c r="E44" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D44" t="n">
+      <c r="F44" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E44" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F44" t="n">
-        <v>7</v>
       </c>
       <c r="G44" t="n">
         <v>24.89659442724458</v>
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="C45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D45" t="n">
+        <v>8</v>
+      </c>
+      <c r="E45" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D45" t="n">
+      <c r="F45" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E45" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F45" t="n">
-        <v>8</v>
       </c>
       <c r="G45" t="n">
         <v>20.86290322580645</v>
@@ -4696,16 +4696,16 @@
         </is>
       </c>
       <c r="C46" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D46" t="n">
+        <v>9</v>
+      </c>
+      <c r="E46" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D46" t="n">
+      <c r="F46" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E46" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F46" t="n">
-        <v>9</v>
       </c>
       <c r="G46" t="n">
         <v>16.15972222222222</v>
@@ -4786,16 +4786,16 @@
         </is>
       </c>
       <c r="C47" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D47" t="n">
+      <c r="F47" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E47" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F47" t="n">
-        <v>10</v>
       </c>
       <c r="G47" t="n">
         <v>12.74865591397849</v>
@@ -4876,16 +4876,16 @@
         </is>
       </c>
       <c r="C48" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D48" t="n">
+        <v>11</v>
+      </c>
+      <c r="E48" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D48" t="n">
+      <c r="F48" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E48" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F48" t="n">
-        <v>11</v>
       </c>
       <c r="G48" t="n">
         <v>8.83611111111111</v>
@@ -4966,16 +4966,16 @@
         </is>
       </c>
       <c r="C49" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D49" t="n">
+        <v>12</v>
+      </c>
+      <c r="E49" t="n">
         <v>49.006733</v>
       </c>
-      <c r="D49" t="n">
+      <c r="F49" t="n">
         <v>2.519843</v>
-      </c>
-      <c r="E49" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F49" t="n">
-        <v>12</v>
       </c>
       <c r="G49" t="n">
         <v>6.840725806451613</v>
@@ -5056,16 +5056,16 @@
         </is>
       </c>
       <c r="C50" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D50" t="n">
+      <c r="F50" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E50" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F50" t="n">
-        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>10.60389784946237</v>
@@ -5152,16 +5152,16 @@
         </is>
       </c>
       <c r="C51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D51" t="n">
+      <c r="F51" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E51" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F51" t="n">
-        <v>2</v>
       </c>
       <c r="G51" t="n">
         <v>11.3078869047619</v>
@@ -5248,16 +5248,16 @@
         </is>
       </c>
       <c r="C52" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D52" t="n">
+      <c r="F52" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E52" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F52" t="n">
-        <v>3</v>
       </c>
       <c r="G52" t="n">
         <v>12.48951612903226</v>
@@ -5344,16 +5344,16 @@
         </is>
       </c>
       <c r="C53" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D53" t="n">
+      <c r="F53" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E53" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F53" t="n">
-        <v>4</v>
       </c>
       <c r="G53" t="n">
         <v>15.68166666666666</v>
@@ -5440,16 +5440,16 @@
         </is>
       </c>
       <c r="C54" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D54" t="n">
+        <v>5</v>
+      </c>
+      <c r="E54" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D54" t="n">
+      <c r="F54" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F54" t="n">
-        <v>5</v>
       </c>
       <c r="G54" t="n">
         <v>18.54811827956989</v>
@@ -5536,16 +5536,16 @@
         </is>
       </c>
       <c r="C55" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D55" t="n">
+        <v>6</v>
+      </c>
+      <c r="E55" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D55" t="n">
+      <c r="F55" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E55" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F55" t="n">
-        <v>6</v>
       </c>
       <c r="G55" t="n">
         <v>24.86986111111111</v>
@@ -5632,16 +5632,16 @@
         </is>
       </c>
       <c r="C56" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D56" t="n">
+        <v>7</v>
+      </c>
+      <c r="E56" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D56" t="n">
+      <c r="F56" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E56" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F56" t="n">
-        <v>7</v>
       </c>
       <c r="G56" t="n">
         <v>25.7114247311828</v>
@@ -5728,16 +5728,16 @@
         </is>
       </c>
       <c r="C57" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D57" t="n">
+        <v>8</v>
+      </c>
+      <c r="E57" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D57" t="n">
+      <c r="F57" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E57" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F57" t="n">
-        <v>8</v>
       </c>
       <c r="G57" t="n">
         <v>26.0375</v>
@@ -5824,16 +5824,16 @@
         </is>
       </c>
       <c r="C58" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D58" t="n">
+        <v>9</v>
+      </c>
+      <c r="E58" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D58" t="n">
+      <c r="F58" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F58" t="n">
-        <v>9</v>
       </c>
       <c r="G58" t="n">
         <v>21.80763888888889</v>
@@ -5920,16 +5920,16 @@
         </is>
       </c>
       <c r="C59" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D59" t="n">
+      <c r="F59" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E59" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F59" t="n">
-        <v>10</v>
       </c>
       <c r="G59" t="n">
         <v>18.24045698924731</v>
@@ -6016,16 +6016,16 @@
         </is>
       </c>
       <c r="C60" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D60" t="n">
+        <v>11</v>
+      </c>
+      <c r="E60" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D60" t="n">
+      <c r="F60" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E60" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F60" t="n">
-        <v>11</v>
       </c>
       <c r="G60" t="n">
         <v>12.89236111111111</v>
@@ -6112,16 +6112,16 @@
         </is>
       </c>
       <c r="C61" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D61" t="n">
+        <v>12</v>
+      </c>
+      <c r="E61" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D61" t="n">
+      <c r="F61" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E61" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F61" t="n">
-        <v>12</v>
       </c>
       <c r="G61" t="n">
         <v>11.55967741935484</v>
@@ -6208,16 +6208,16 @@
         </is>
       </c>
       <c r="C62" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E62" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
       </c>
       <c r="G62" t="n">
         <v>9.45483870967742</v>
@@ -6304,16 +6304,16 @@
         </is>
       </c>
       <c r="C63" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D63" t="n">
+      <c r="F63" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E63" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F63" t="n">
-        <v>2</v>
       </c>
       <c r="G63" t="n">
         <v>11.85342261904762</v>
@@ -6400,16 +6400,16 @@
         </is>
       </c>
       <c r="C64" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D64" t="n">
+      <c r="F64" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E64" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F64" t="n">
-        <v>3</v>
       </c>
       <c r="G64" t="n">
         <v>13.10672043010753</v>
@@ -6496,16 +6496,16 @@
         </is>
       </c>
       <c r="C65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4</v>
+      </c>
+      <c r="E65" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D65" t="n">
+      <c r="F65" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E65" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F65" t="n">
-        <v>4</v>
       </c>
       <c r="G65" t="n">
         <v>16.37541666666667</v>
@@ -6592,16 +6592,16 @@
         </is>
       </c>
       <c r="C66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D66" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D66" t="n">
+      <c r="F66" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E66" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F66" t="n">
-        <v>5</v>
       </c>
       <c r="G66" t="n">
         <v>19.46653225806451</v>
@@ -6688,16 +6688,16 @@
         </is>
       </c>
       <c r="C67" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D67" t="n">
+      <c r="F67" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E67" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F67" t="n">
-        <v>6</v>
       </c>
       <c r="G67" t="n">
         <v>24.67680555555555</v>
@@ -6784,16 +6784,16 @@
         </is>
       </c>
       <c r="C68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D68" t="n">
+        <v>7</v>
+      </c>
+      <c r="E68" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D68" t="n">
+      <c r="F68" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E68" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F68" t="n">
-        <v>7</v>
       </c>
       <c r="G68" t="n">
         <v>27.16160990712075</v>
@@ -6880,16 +6880,16 @@
         </is>
       </c>
       <c r="C69" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D69" t="n">
+        <v>8</v>
+      </c>
+      <c r="E69" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D69" t="n">
+      <c r="F69" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E69" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F69" t="n">
-        <v>8</v>
       </c>
       <c r="G69" t="n">
         <v>26.0375</v>
@@ -6976,16 +6976,16 @@
         </is>
       </c>
       <c r="C70" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D70" t="n">
+        <v>9</v>
+      </c>
+      <c r="E70" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D70" t="n">
+      <c r="F70" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E70" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F70" t="n">
-        <v>9</v>
       </c>
       <c r="G70" t="n">
         <v>21.80763888888889</v>
@@ -7072,16 +7072,16 @@
         </is>
       </c>
       <c r="C71" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D71" t="n">
+      <c r="F71" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E71" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F71" t="n">
-        <v>10</v>
       </c>
       <c r="G71" t="n">
         <v>18.24045698924731</v>
@@ -7168,16 +7168,16 @@
         </is>
       </c>
       <c r="C72" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D72" t="n">
+        <v>11</v>
+      </c>
+      <c r="E72" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D72" t="n">
+      <c r="F72" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E72" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F72" t="n">
-        <v>11</v>
       </c>
       <c r="G72" t="n">
         <v>12.89236111111111</v>
@@ -7264,16 +7264,16 @@
         </is>
       </c>
       <c r="C73" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D73" t="n">
+        <v>12</v>
+      </c>
+      <c r="E73" t="n">
         <v>43.689186</v>
       </c>
-      <c r="D73" t="n">
+      <c r="F73" t="n">
         <v>7.240512</v>
-      </c>
-      <c r="E73" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F73" t="n">
-        <v>12</v>
       </c>
       <c r="G73" t="n">
         <v>11.55967741935484</v>
@@ -7360,16 +7360,16 @@
         </is>
       </c>
       <c r="C74" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D74" t="n">
+      <c r="F74" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E74" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F74" t="n">
-        <v>1</v>
       </c>
       <c r="G74" t="n">
         <v>4.338978494623656</v>
@@ -7456,16 +7456,16 @@
         </is>
       </c>
       <c r="C75" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D75" t="n">
+      <c r="F75" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E75" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F75" t="n">
-        <v>2</v>
       </c>
       <c r="G75" t="n">
         <v>4.786011904761905</v>
@@ -7552,16 +7552,16 @@
         </is>
       </c>
       <c r="C76" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D76" t="n">
+      <c r="F76" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E76" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F76" t="n">
-        <v>3</v>
       </c>
       <c r="G76" t="n">
         <v>8.272446236559139</v>
@@ -7648,16 +7648,16 @@
         </is>
       </c>
       <c r="C77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D77" t="n">
+      <c r="F77" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E77" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F77" t="n">
-        <v>4</v>
       </c>
       <c r="G77" t="n">
         <v>13.05652777777778</v>
@@ -7744,16 +7744,16 @@
         </is>
       </c>
       <c r="C78" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D78" t="n">
+        <v>5</v>
+      </c>
+      <c r="E78" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D78" t="n">
+      <c r="F78" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E78" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F78" t="n">
-        <v>5</v>
       </c>
       <c r="G78" t="n">
         <v>16.08051075268817</v>
@@ -7840,16 +7840,16 @@
         </is>
       </c>
       <c r="C79" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D79" t="n">
+        <v>6</v>
+      </c>
+      <c r="E79" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D79" t="n">
+      <c r="F79" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E79" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F79" t="n">
-        <v>6</v>
       </c>
       <c r="G79" t="n">
         <v>21.65291666666667</v>
@@ -7936,16 +7936,16 @@
         </is>
       </c>
       <c r="C80" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D80" t="n">
+        <v>7</v>
+      </c>
+      <c r="E80" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D80" t="n">
+      <c r="F80" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E80" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F80" t="n">
-        <v>7</v>
       </c>
       <c r="G80" t="n">
         <v>20.70013440860215</v>
@@ -8032,16 +8032,16 @@
         </is>
       </c>
       <c r="C81" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D81" t="n">
+        <v>8</v>
+      </c>
+      <c r="E81" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D81" t="n">
+      <c r="F81" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E81" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F81" t="n">
-        <v>8</v>
       </c>
       <c r="G81" t="n">
         <v>21.14408602150537</v>
@@ -8128,16 +8128,16 @@
         </is>
       </c>
       <c r="C82" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D82" t="n">
+        <v>9</v>
+      </c>
+      <c r="E82" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D82" t="n">
+      <c r="F82" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E82" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F82" t="n">
-        <v>9</v>
       </c>
       <c r="G82" t="n">
         <v>15.73041666666667</v>
@@ -8224,16 +8224,16 @@
         </is>
       </c>
       <c r="C83" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D83" t="n">
+      <c r="F83" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E83" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F83" t="n">
-        <v>10</v>
       </c>
       <c r="G83" t="n">
         <v>12.45094086021505</v>
@@ -8320,16 +8320,16 @@
         </is>
       </c>
       <c r="C84" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D84" t="n">
+        <v>11</v>
+      </c>
+      <c r="E84" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D84" t="n">
+      <c r="F84" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E84" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F84" t="n">
-        <v>11</v>
       </c>
       <c r="G84" t="n">
         <v>8.55486111111111</v>
@@ -8416,16 +8416,16 @@
         </is>
       </c>
       <c r="C85" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D85" t="n">
+        <v>12</v>
+      </c>
+      <c r="E85" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D85" t="n">
+      <c r="F85" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E85" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F85" t="n">
-        <v>12</v>
       </c>
       <c r="G85" t="n">
         <v>6.360618279569893</v>
@@ -8512,16 +8512,16 @@
         </is>
       </c>
       <c r="C86" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D86" t="n">
+      <c r="F86" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E86" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F86" t="n">
-        <v>1</v>
       </c>
       <c r="G86" t="n">
         <v>4.91989247311828</v>
@@ -8608,16 +8608,16 @@
         </is>
       </c>
       <c r="C87" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D87" t="n">
+      <c r="F87" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E87" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F87" t="n">
-        <v>2</v>
       </c>
       <c r="G87" t="n">
         <v>8.488095238095237</v>
@@ -8704,16 +8704,16 @@
         </is>
       </c>
       <c r="C88" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3</v>
+      </c>
+      <c r="E88" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D88" t="n">
+      <c r="F88" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E88" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F88" t="n">
-        <v>3</v>
       </c>
       <c r="G88" t="n">
         <v>9.261290322580646</v>
@@ -8800,16 +8800,16 @@
         </is>
       </c>
       <c r="C89" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D89" t="n">
+        <v>4</v>
+      </c>
+      <c r="E89" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D89" t="n">
+      <c r="F89" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E89" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F89" t="n">
-        <v>4</v>
       </c>
       <c r="G89" t="n">
         <v>13.29361111111111</v>
@@ -8896,16 +8896,16 @@
         </is>
       </c>
       <c r="C90" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D90" t="n">
+        <v>5</v>
+      </c>
+      <c r="E90" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D90" t="n">
+      <c r="F90" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E90" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F90" t="n">
-        <v>5</v>
       </c>
       <c r="G90" t="n">
         <v>16.67110215053764</v>
@@ -8992,16 +8992,16 @@
         </is>
       </c>
       <c r="C91" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D91" t="n">
+        <v>6</v>
+      </c>
+      <c r="E91" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D91" t="n">
+      <c r="F91" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E91" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F91" t="n">
-        <v>6</v>
       </c>
       <c r="G91" t="n">
         <v>22.68513888888889</v>
@@ -9088,16 +9088,16 @@
         </is>
       </c>
       <c r="C92" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D92" t="n">
+        <v>7</v>
+      </c>
+      <c r="E92" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D92" t="n">
+      <c r="F92" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E92" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F92" t="n">
-        <v>7</v>
       </c>
       <c r="G92" t="n">
         <v>25.78049535603715</v>
@@ -9184,16 +9184,16 @@
         </is>
       </c>
       <c r="C93" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D93" t="n">
+        <v>8</v>
+      </c>
+      <c r="E93" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D93" t="n">
+      <c r="F93" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E93" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F93" t="n">
-        <v>8</v>
       </c>
       <c r="G93" t="n">
         <v>21.14408602150537</v>
@@ -9280,16 +9280,16 @@
         </is>
       </c>
       <c r="C94" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D94" t="n">
+        <v>9</v>
+      </c>
+      <c r="E94" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D94" t="n">
+      <c r="F94" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E94" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F94" t="n">
-        <v>9</v>
       </c>
       <c r="G94" t="n">
         <v>15.73041666666667</v>
@@ -9376,16 +9376,16 @@
         </is>
       </c>
       <c r="C95" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D95" t="n">
+      <c r="F95" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E95" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F95" t="n">
-        <v>10</v>
       </c>
       <c r="G95" t="n">
         <v>12.45094086021505</v>
@@ -9472,16 +9472,16 @@
         </is>
       </c>
       <c r="C96" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D96" t="n">
+        <v>11</v>
+      </c>
+      <c r="E96" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D96" t="n">
+      <c r="F96" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E96" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F96" t="n">
-        <v>11</v>
       </c>
       <c r="G96" t="n">
         <v>8.55486111111111</v>
@@ -9568,16 +9568,16 @@
         </is>
       </c>
       <c r="C97" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D97" t="n">
+        <v>12</v>
+      </c>
+      <c r="E97" t="n">
         <v>48.849778</v>
       </c>
-      <c r="D97" t="n">
+      <c r="F97" t="n">
         <v>2.282836</v>
-      </c>
-      <c r="E97" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F97" t="n">
-        <v>12</v>
       </c>
       <c r="G97" t="n">
         <v>6.360618279569893</v>
@@ -9664,16 +9664,16 @@
         </is>
       </c>
       <c r="C98" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+      <c r="E98" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D98" t="n">
+      <c r="F98" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E98" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F98" t="n">
-        <v>1</v>
       </c>
       <c r="G98" t="n">
         <v>4.338978494623656</v>
@@ -9760,16 +9760,16 @@
         </is>
       </c>
       <c r="C99" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D99" t="n">
+        <v>2</v>
+      </c>
+      <c r="E99" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D99" t="n">
+      <c r="F99" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E99" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F99" t="n">
-        <v>2</v>
       </c>
       <c r="G99" t="n">
         <v>4.786011904761905</v>
@@ -9856,16 +9856,16 @@
         </is>
       </c>
       <c r="C100" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D100" t="n">
+      <c r="F100" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E100" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F100" t="n">
-        <v>3</v>
       </c>
       <c r="G100" t="n">
         <v>8.272446236559139</v>
@@ -9952,16 +9952,16 @@
         </is>
       </c>
       <c r="C101" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D101" t="n">
+        <v>4</v>
+      </c>
+      <c r="E101" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D101" t="n">
+      <c r="F101" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E101" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F101" t="n">
-        <v>4</v>
       </c>
       <c r="G101" t="n">
         <v>13.05652777777778</v>
@@ -10048,16 +10048,16 @@
         </is>
       </c>
       <c r="C102" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D102" t="n">
+        <v>5</v>
+      </c>
+      <c r="E102" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D102" t="n">
+      <c r="F102" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E102" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F102" t="n">
-        <v>5</v>
       </c>
       <c r="G102" t="n">
         <v>16.08051075268817</v>
@@ -10144,16 +10144,16 @@
         </is>
       </c>
       <c r="C103" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D103" t="n">
+        <v>6</v>
+      </c>
+      <c r="E103" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D103" t="n">
+      <c r="F103" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E103" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F103" t="n">
-        <v>6</v>
       </c>
       <c r="G103" t="n">
         <v>21.65291666666667</v>
@@ -10240,16 +10240,16 @@
         </is>
       </c>
       <c r="C104" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D104" t="n">
+        <v>7</v>
+      </c>
+      <c r="E104" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D104" t="n">
+      <c r="F104" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E104" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F104" t="n">
-        <v>7</v>
       </c>
       <c r="G104" t="n">
         <v>20.70013440860215</v>
@@ -10336,16 +10336,16 @@
         </is>
       </c>
       <c r="C105" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D105" t="n">
+        <v>8</v>
+      </c>
+      <c r="E105" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D105" t="n">
+      <c r="F105" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E105" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F105" t="n">
-        <v>8</v>
       </c>
       <c r="G105" t="n">
         <v>21.14408602150537</v>
@@ -10432,16 +10432,16 @@
         </is>
       </c>
       <c r="C106" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D106" t="n">
+        <v>9</v>
+      </c>
+      <c r="E106" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D106" t="n">
+      <c r="F106" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E106" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F106" t="n">
-        <v>9</v>
       </c>
       <c r="G106" t="n">
         <v>15.73041666666667</v>
@@ -10528,16 +10528,16 @@
         </is>
       </c>
       <c r="C107" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D107" t="n">
+        <v>10</v>
+      </c>
+      <c r="E107" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D107" t="n">
+      <c r="F107" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E107" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F107" t="n">
-        <v>10</v>
       </c>
       <c r="G107" t="n">
         <v>12.45094086021505</v>
@@ -10624,16 +10624,16 @@
         </is>
       </c>
       <c r="C108" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D108" t="n">
+        <v>11</v>
+      </c>
+      <c r="E108" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D108" t="n">
+      <c r="F108" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E108" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F108" t="n">
-        <v>11</v>
       </c>
       <c r="G108" t="n">
         <v>8.55486111111111</v>
@@ -10720,16 +10720,16 @@
         </is>
       </c>
       <c r="C109" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D109" t="n">
+        <v>12</v>
+      </c>
+      <c r="E109" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D109" t="n">
+      <c r="F109" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E109" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F109" t="n">
-        <v>12</v>
       </c>
       <c r="G109" t="n">
         <v>6.360618279569893</v>
@@ -10816,16 +10816,16 @@
         </is>
       </c>
       <c r="C110" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D110" t="n">
+      <c r="F110" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E110" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F110" t="n">
-        <v>1</v>
       </c>
       <c r="G110" t="n">
         <v>4.91989247311828</v>
@@ -10912,16 +10912,16 @@
         </is>
       </c>
       <c r="C111" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D111" t="n">
+      <c r="F111" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E111" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F111" t="n">
-        <v>2</v>
       </c>
       <c r="G111" t="n">
         <v>8.488095238095237</v>
@@ -11008,16 +11008,16 @@
         </is>
       </c>
       <c r="C112" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D112" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D112" t="n">
+      <c r="F112" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E112" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F112" t="n">
-        <v>3</v>
       </c>
       <c r="G112" t="n">
         <v>9.261290322580646</v>
@@ -11104,16 +11104,16 @@
         </is>
       </c>
       <c r="C113" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D113" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D113" t="n">
+      <c r="F113" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E113" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F113" t="n">
-        <v>4</v>
       </c>
       <c r="G113" t="n">
         <v>13.29361111111111</v>
@@ -11200,16 +11200,16 @@
         </is>
       </c>
       <c r="C114" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D114" t="n">
+        <v>5</v>
+      </c>
+      <c r="E114" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D114" t="n">
+      <c r="F114" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E114" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F114" t="n">
-        <v>5</v>
       </c>
       <c r="G114" t="n">
         <v>16.67110215053764</v>
@@ -11296,16 +11296,16 @@
         </is>
       </c>
       <c r="C115" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D115" t="n">
+        <v>6</v>
+      </c>
+      <c r="E115" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D115" t="n">
+      <c r="F115" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E115" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F115" t="n">
-        <v>6</v>
       </c>
       <c r="G115" t="n">
         <v>22.68513888888889</v>
@@ -11392,16 +11392,16 @@
         </is>
       </c>
       <c r="C116" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D116" t="n">
+        <v>7</v>
+      </c>
+      <c r="E116" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D116" t="n">
+      <c r="F116" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E116" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F116" t="n">
-        <v>7</v>
       </c>
       <c r="G116" t="n">
         <v>25.78049535603715</v>
@@ -11488,16 +11488,16 @@
         </is>
       </c>
       <c r="C117" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D117" t="n">
+        <v>8</v>
+      </c>
+      <c r="E117" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D117" t="n">
+      <c r="F117" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E117" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F117" t="n">
-        <v>8</v>
       </c>
       <c r="G117" t="n">
         <v>21.14408602150537</v>
@@ -11584,16 +11584,16 @@
         </is>
       </c>
       <c r="C118" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D118" t="n">
+        <v>9</v>
+      </c>
+      <c r="E118" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D118" t="n">
+      <c r="F118" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E118" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F118" t="n">
-        <v>9</v>
       </c>
       <c r="G118" t="n">
         <v>15.73041666666667</v>
@@ -11680,16 +11680,16 @@
         </is>
       </c>
       <c r="C119" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D119" t="n">
+        <v>10</v>
+      </c>
+      <c r="E119" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D119" t="n">
+      <c r="F119" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E119" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F119" t="n">
-        <v>10</v>
       </c>
       <c r="G119" t="n">
         <v>12.45094086021505</v>
@@ -11776,16 +11776,16 @@
         </is>
       </c>
       <c r="C120" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D120" t="n">
+        <v>11</v>
+      </c>
+      <c r="E120" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D120" t="n">
+      <c r="F120" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E120" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F120" t="n">
-        <v>11</v>
       </c>
       <c r="G120" t="n">
         <v>8.55486111111111</v>
@@ -11872,16 +11872,16 @@
         </is>
       </c>
       <c r="C121" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D121" t="n">
+        <v>12</v>
+      </c>
+      <c r="E121" t="n">
         <v>48.833827</v>
       </c>
-      <c r="D121" t="n">
+      <c r="F121" t="n">
         <v>2.256274</v>
-      </c>
-      <c r="E121" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F121" t="n">
-        <v>12</v>
       </c>
       <c r="G121" t="n">
         <v>6.360618279569893</v>
@@ -11968,16 +11968,16 @@
         </is>
       </c>
       <c r="C122" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D122" t="n">
+      <c r="F122" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E122" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F122" t="n">
-        <v>1</v>
       </c>
       <c r="G122" t="n">
         <v>0.6228494623655914</v>
@@ -12058,16 +12058,16 @@
         </is>
       </c>
       <c r="C123" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2</v>
+      </c>
+      <c r="E123" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D123" t="n">
+      <c r="F123" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E123" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F123" t="n">
-        <v>2</v>
       </c>
       <c r="G123" t="n">
         <v>1.727827380952381</v>
@@ -12148,16 +12148,16 @@
         </is>
       </c>
       <c r="C124" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3</v>
+      </c>
+      <c r="E124" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D124" t="n">
+      <c r="F124" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E124" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F124" t="n">
-        <v>3</v>
       </c>
       <c r="G124" t="n">
         <v>3.30510752688172</v>
@@ -12238,16 +12238,16 @@
         </is>
       </c>
       <c r="C125" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D125" t="n">
+        <v>4</v>
+      </c>
+      <c r="E125" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D125" t="n">
+      <c r="F125" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E125" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F125" t="n">
-        <v>4</v>
       </c>
       <c r="G125" t="n">
         <v>7.325277777777777</v>
@@ -12328,16 +12328,16 @@
         </is>
       </c>
       <c r="C126" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D126" t="n">
+        <v>5</v>
+      </c>
+      <c r="E126" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D126" t="n">
+      <c r="F126" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E126" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F126" t="n">
-        <v>5</v>
       </c>
       <c r="G126" t="n">
         <v>9.192607526881721</v>
@@ -12418,16 +12418,16 @@
         </is>
       </c>
       <c r="C127" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D127" t="n">
+        <v>6</v>
+      </c>
+      <c r="E127" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D127" t="n">
+      <c r="F127" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E127" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F127" t="n">
-        <v>6</v>
       </c>
       <c r="G127" t="n">
         <v>15.40902777777778</v>
@@ -12508,16 +12508,16 @@
         </is>
       </c>
       <c r="C128" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D128" t="n">
+        <v>7</v>
+      </c>
+      <c r="E128" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D128" t="n">
+      <c r="F128" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E128" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F128" t="n">
-        <v>7</v>
       </c>
       <c r="G128" t="n">
         <v>14.2364247311828</v>
@@ -12598,16 +12598,16 @@
         </is>
       </c>
       <c r="C129" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D129" t="n">
+        <v>8</v>
+      </c>
+      <c r="E129" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D129" t="n">
+      <c r="F129" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E129" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F129" t="n">
-        <v>8</v>
       </c>
       <c r="G129" t="n">
         <v>16.12298387096774</v>
@@ -12688,16 +12688,16 @@
         </is>
       </c>
       <c r="C130" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D130" t="n">
+        <v>9</v>
+      </c>
+      <c r="E130" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D130" t="n">
+      <c r="F130" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E130" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F130" t="n">
-        <v>9</v>
       </c>
       <c r="G130" t="n">
         <v>12.08972222222222</v>
@@ -12778,16 +12778,16 @@
         </is>
       </c>
       <c r="C131" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D131" t="n">
+        <v>10</v>
+      </c>
+      <c r="E131" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D131" t="n">
+      <c r="F131" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E131" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F131" t="n">
-        <v>10</v>
       </c>
       <c r="G131" t="n">
         <v>8.104569892473119</v>
@@ -12868,16 +12868,16 @@
         </is>
       </c>
       <c r="C132" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D132" t="n">
+        <v>11</v>
+      </c>
+      <c r="E132" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D132" t="n">
+      <c r="F132" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E132" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F132" t="n">
-        <v>11</v>
       </c>
       <c r="G132" t="n">
         <v>2.563333333333333</v>
@@ -12958,16 +12958,16 @@
         </is>
       </c>
       <c r="C133" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D133" t="n">
+        <v>12</v>
+      </c>
+      <c r="E133" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D133" t="n">
+      <c r="F133" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E133" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F133" t="n">
-        <v>12</v>
       </c>
       <c r="G133" t="n">
         <v>2.668010752688172</v>
@@ -13048,16 +13048,16 @@
         </is>
       </c>
       <c r="C134" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D134" t="n">
+      <c r="F134" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E134" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F134" t="n">
-        <v>1</v>
       </c>
       <c r="G134" t="n">
         <v>-1.768010752688172</v>
@@ -13138,16 +13138,16 @@
         </is>
       </c>
       <c r="C135" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2</v>
+      </c>
+      <c r="E135" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D135" t="n">
+      <c r="F135" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E135" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F135" t="n">
-        <v>2</v>
       </c>
       <c r="G135" t="n">
         <v>1.950297619047619</v>
@@ -13228,16 +13228,16 @@
         </is>
       </c>
       <c r="C136" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3</v>
+      </c>
+      <c r="E136" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D136" t="n">
+      <c r="F136" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E136" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F136" t="n">
-        <v>3</v>
       </c>
       <c r="G136" t="n">
         <v>1.908064516129032</v>
@@ -13318,16 +13318,16 @@
         </is>
       </c>
       <c r="C137" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D137" t="n">
+        <v>4</v>
+      </c>
+      <c r="E137" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D137" t="n">
+      <c r="F137" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E137" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F137" t="n">
-        <v>4</v>
       </c>
       <c r="G137" t="n">
         <v>8.072222222222223</v>
@@ -13408,16 +13408,16 @@
         </is>
       </c>
       <c r="C138" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D138" t="n">
+        <v>5</v>
+      </c>
+      <c r="E138" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D138" t="n">
+      <c r="F138" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E138" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F138" t="n">
-        <v>5</v>
       </c>
       <c r="G138" t="n">
         <v>9.798924731182796</v>
@@ -13498,16 +13498,16 @@
         </is>
       </c>
       <c r="C139" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D139" t="n">
+        <v>6</v>
+      </c>
+      <c r="E139" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D139" t="n">
+      <c r="F139" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E139" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F139" t="n">
-        <v>6</v>
       </c>
       <c r="G139" t="n">
         <v>16.09930555555556</v>
@@ -13588,16 +13588,16 @@
         </is>
       </c>
       <c r="C140" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D140" t="n">
+        <v>7</v>
+      </c>
+      <c r="E140" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D140" t="n">
+      <c r="F140" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E140" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F140" t="n">
-        <v>7</v>
       </c>
       <c r="G140" t="n">
         <v>18.33065015479876</v>
@@ -13678,16 +13678,16 @@
         </is>
       </c>
       <c r="C141" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D141" t="n">
+        <v>8</v>
+      </c>
+      <c r="E141" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D141" t="n">
+      <c r="F141" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E141" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F141" t="n">
-        <v>8</v>
       </c>
       <c r="G141" t="n">
         <v>16.12298387096774</v>
@@ -13768,16 +13768,16 @@
         </is>
       </c>
       <c r="C142" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D142" t="n">
+        <v>9</v>
+      </c>
+      <c r="E142" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D142" t="n">
+      <c r="F142" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E142" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F142" t="n">
-        <v>9</v>
       </c>
       <c r="G142" t="n">
         <v>12.08972222222222</v>
@@ -13858,16 +13858,16 @@
         </is>
       </c>
       <c r="C143" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D143" t="n">
+        <v>10</v>
+      </c>
+      <c r="E143" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D143" t="n">
+      <c r="F143" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E143" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F143" t="n">
-        <v>10</v>
       </c>
       <c r="G143" t="n">
         <v>8.104569892473119</v>
@@ -13948,16 +13948,16 @@
         </is>
       </c>
       <c r="C144" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D144" t="n">
+        <v>11</v>
+      </c>
+      <c r="E144" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D144" t="n">
+      <c r="F144" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E144" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F144" t="n">
-        <v>11</v>
       </c>
       <c r="G144" t="n">
         <v>2.563333333333333</v>
@@ -14038,16 +14038,16 @@
         </is>
       </c>
       <c r="C145" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D145" t="n">
+        <v>12</v>
+      </c>
+      <c r="E145" t="n">
         <v>45.8591651916</v>
       </c>
-      <c r="D145" t="n">
+      <c r="F145" t="n">
         <v>6.6190552711</v>
-      </c>
-      <c r="E145" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F145" t="n">
-        <v>12</v>
       </c>
       <c r="G145" t="n">
         <v>2.668010752688172</v>
@@ -14128,16 +14128,16 @@
         </is>
       </c>
       <c r="C146" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D146" t="n">
+      <c r="F146" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E146" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F146" t="n">
-        <v>1</v>
       </c>
       <c r="G146" t="n">
         <v>3.29247311827957</v>
@@ -14224,16 +14224,16 @@
         </is>
       </c>
       <c r="C147" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D147" t="n">
+        <v>2</v>
+      </c>
+      <c r="E147" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D147" t="n">
+      <c r="F147" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E147" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F147" t="n">
-        <v>2</v>
       </c>
       <c r="G147" t="n">
         <v>3.3625</v>
@@ -14320,16 +14320,16 @@
         </is>
       </c>
       <c r="C148" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3</v>
+      </c>
+      <c r="E148" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D148" t="n">
+      <c r="F148" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E148" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F148" t="n">
-        <v>3</v>
       </c>
       <c r="G148" t="n">
         <v>6.74260752688172</v>
@@ -14416,16 +14416,16 @@
         </is>
       </c>
       <c r="C149" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D149" t="n">
+        <v>4</v>
+      </c>
+      <c r="E149" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D149" t="n">
+      <c r="F149" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E149" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F149" t="n">
-        <v>4</v>
       </c>
       <c r="G149" t="n">
         <v>11.43972222222222</v>
@@ -14512,16 +14512,16 @@
         </is>
       </c>
       <c r="C150" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D150" t="n">
+        <v>5</v>
+      </c>
+      <c r="E150" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D150" t="n">
+      <c r="F150" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E150" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F150" t="n">
-        <v>5</v>
       </c>
       <c r="G150" t="n">
         <v>15.14072580645161</v>
@@ -14608,16 +14608,16 @@
         </is>
       </c>
       <c r="C151" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D151" t="n">
+        <v>6</v>
+      </c>
+      <c r="E151" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D151" t="n">
+      <c r="F151" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E151" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F151" t="n">
-        <v>6</v>
       </c>
       <c r="G151" t="n">
         <v>21.08069444444444</v>
@@ -14704,16 +14704,16 @@
         </is>
       </c>
       <c r="C152" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D152" t="n">
+        <v>7</v>
+      </c>
+      <c r="E152" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D152" t="n">
+      <c r="F152" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E152" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F152" t="n">
-        <v>7</v>
       </c>
       <c r="G152" t="n">
         <v>20.14583333333333</v>
@@ -14800,16 +14800,16 @@
         </is>
       </c>
       <c r="C153" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D153" t="n">
+        <v>8</v>
+      </c>
+      <c r="E153" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D153" t="n">
+      <c r="F153" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E153" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F153" t="n">
-        <v>8</v>
       </c>
       <c r="G153" t="n">
         <v>19.82809139784946</v>
@@ -14896,16 +14896,16 @@
         </is>
       </c>
       <c r="C154" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D154" t="n">
+        <v>9</v>
+      </c>
+      <c r="E154" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D154" t="n">
+      <c r="F154" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E154" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F154" t="n">
-        <v>9</v>
       </c>
       <c r="G154" t="n">
         <v>15.65944444444444</v>
@@ -14992,16 +14992,16 @@
         </is>
       </c>
       <c r="C155" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D155" t="n">
+        <v>10</v>
+      </c>
+      <c r="E155" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D155" t="n">
+      <c r="F155" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E155" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F155" t="n">
-        <v>10</v>
       </c>
       <c r="G155" t="n">
         <v>11.10967741935484</v>
@@ -15088,16 +15088,16 @@
         </is>
       </c>
       <c r="C156" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D156" t="n">
+        <v>11</v>
+      </c>
+      <c r="E156" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D156" t="n">
+      <c r="F156" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E156" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F156" t="n">
-        <v>11</v>
       </c>
       <c r="G156" t="n">
         <v>6.025</v>
@@ -15184,16 +15184,16 @@
         </is>
       </c>
       <c r="C157" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D157" t="n">
+        <v>12</v>
+      </c>
+      <c r="E157" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D157" t="n">
+      <c r="F157" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E157" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F157" t="n">
-        <v>12</v>
       </c>
       <c r="G157" t="n">
         <v>3.193682795698925</v>
@@ -15280,16 +15280,16 @@
         </is>
       </c>
       <c r="C158" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
+      </c>
+      <c r="E158" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D158" t="n">
+      <c r="F158" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E158" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F158" t="n">
-        <v>1</v>
       </c>
       <c r="G158" t="n">
         <v>1.329032258064516</v>
@@ -15376,16 +15376,16 @@
         </is>
       </c>
       <c r="C159" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2</v>
+      </c>
+      <c r="E159" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D159" t="n">
+      <c r="F159" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E159" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F159" t="n">
-        <v>2</v>
       </c>
       <c r="G159" t="n">
         <v>6.108630952380953</v>
@@ -15472,16 +15472,16 @@
         </is>
       </c>
       <c r="C160" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D160" t="n">
+        <v>3</v>
+      </c>
+      <c r="E160" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D160" t="n">
+      <c r="F160" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E160" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F160" t="n">
-        <v>3</v>
       </c>
       <c r="G160" t="n">
         <v>7.057526881720429</v>
@@ -15568,16 +15568,16 @@
         </is>
       </c>
       <c r="C161" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D161" t="n">
+        <v>4</v>
+      </c>
+      <c r="E161" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D161" t="n">
+      <c r="F161" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E161" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F161" t="n">
-        <v>4</v>
       </c>
       <c r="G161" t="n">
         <v>11.52458333333333</v>
@@ -15664,16 +15664,16 @@
         </is>
       </c>
       <c r="C162" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D162" t="n">
+        <v>5</v>
+      </c>
+      <c r="E162" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D162" t="n">
+      <c r="F162" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E162" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F162" t="n">
-        <v>5</v>
       </c>
       <c r="G162" t="n">
         <v>16.10013440860215</v>
@@ -15760,16 +15760,16 @@
         </is>
       </c>
       <c r="C163" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D163" t="n">
+        <v>6</v>
+      </c>
+      <c r="E163" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D163" t="n">
+      <c r="F163" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E163" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F163" t="n">
-        <v>6</v>
       </c>
       <c r="G163" t="n">
         <v>22.26347222222222</v>
@@ -15856,16 +15856,16 @@
         </is>
       </c>
       <c r="C164" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D164" t="n">
+        <v>7</v>
+      </c>
+      <c r="E164" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D164" t="n">
+      <c r="F164" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E164" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F164" t="n">
-        <v>7</v>
       </c>
       <c r="G164" t="n">
         <v>24.5030959752322</v>
@@ -15952,16 +15952,16 @@
         </is>
       </c>
       <c r="C165" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D165" t="n">
+        <v>8</v>
+      </c>
+      <c r="E165" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D165" t="n">
+      <c r="F165" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E165" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F165" t="n">
-        <v>8</v>
       </c>
       <c r="G165" t="n">
         <v>19.82809139784946</v>
@@ -16048,16 +16048,16 @@
         </is>
       </c>
       <c r="C166" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D166" t="n">
+        <v>9</v>
+      </c>
+      <c r="E166" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D166" t="n">
+      <c r="F166" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E166" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F166" t="n">
-        <v>9</v>
       </c>
       <c r="G166" t="n">
         <v>15.65944444444444</v>
@@ -16144,16 +16144,16 @@
         </is>
       </c>
       <c r="C167" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D167" t="n">
+        <v>10</v>
+      </c>
+      <c r="E167" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D167" t="n">
+      <c r="F167" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E167" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F167" t="n">
-        <v>10</v>
       </c>
       <c r="G167" t="n">
         <v>11.10967741935484</v>
@@ -16240,16 +16240,16 @@
         </is>
       </c>
       <c r="C168" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D168" t="n">
+        <v>11</v>
+      </c>
+      <c r="E168" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D168" t="n">
+      <c r="F168" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E168" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F168" t="n">
-        <v>11</v>
       </c>
       <c r="G168" t="n">
         <v>6.025</v>
@@ -16336,16 +16336,16 @@
         </is>
       </c>
       <c r="C169" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D169" t="n">
+        <v>12</v>
+      </c>
+      <c r="E169" t="n">
         <v>48.591522</v>
       </c>
-      <c r="D169" t="n">
+      <c r="F169" t="n">
         <v>7.754599</v>
-      </c>
-      <c r="E169" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F169" t="n">
-        <v>12</v>
       </c>
       <c r="G169" t="n">
         <v>3.193682795698925</v>
